--- a/test_data/WTA/WTA Calculator - Interest And Penalties/WTA Calculator - Interest And Penalties_Test_Cases.xlsx
+++ b/test_data/WTA/WTA Calculator - Interest And Penalties/WTA Calculator - Interest And Penalties_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -628,7 +628,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>IAP_03</t>
+          <t>IAP_10</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -638,12 +638,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>'Source Jurisdiction' lists real countries</t>
+          <t>Switching to 'By Entity' swaps in Corporate Group fields</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Opening 'Source Jurisdiction' must list real country names including Bangladesh.</t>
+          <t>Clicking 'By Entity' must swap 'Source Jurisdiction' for 'Corporate Group'.</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -659,23 +659,23 @@
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Interest And Penalties
-2. Open 'Source Jurisdiction'
-3. Verify real countries are listed</t>
+2. Click 'By Entity'
+3. Verify 'Corporate Group' field is visible</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Opening 'Source Jurisdiction' must list real country names including Bangladesh.</t>
+          <t>Clicking 'By Entity' must swap 'Source Jurisdiction' for 'Corporate Group'.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>'Source Jurisdiction' correctly lists 120 real countries.</t>
+          <t>Switching to 'By Entity' correctly swapped in the entity-based field.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>[PASS] 'Source Jurisdiction' lists real countries including Bangladesh</t>
+          <t>[PASS] 'By Entity' mode shows the 'Corporate Group' field</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -687,7 +687,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>IAP_04</t>
+          <t>IAP_12</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -697,12 +697,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>A jurisdiction/year with no offence data disables 'Type of offences'</t>
+          <t>'Start over' shows a confirmation dialog</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Selecting Australia / 01 July 2023-30 June 2024 (a confirmed live null-AllOffense combination) must leave 'Type of offences' disabled, showing 'No offenses available' - this is real, documented application behavior, not an automation bug.</t>
+          <t>Clicking 'Start over' must show a confirmation dialog reading 'Are you sure to reset all your selections?' with Cancel/Yes actions.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -712,560 +712,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Source Jurisdiction: Australia, Tax Year: 01 July 2023 - 30 June 2024</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open Interest And Penalties, select Australia / 2023-2024
-2. Verify 'Type of offences' is disabled showing 'No offenses available'</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Selecting Australia / 01 July 2023-30 June 2024 (a confirmed live null-AllOffense combination) must leave 'Type of offences' disabled, showing 'No offenses available' - this is real, documented application behavior, not an automation bug.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>'Type of offences' correctly showed the real no-data state for this jurisdiction/year.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'Type of offences' is disabled with the expected placeholder</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>IAP_05</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Interest And Penalties</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Bangladesh/2023-2024 lists the real 'Late payment' offence</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Selecting Bangladesh / 01 July 2023-30 June 2024 must enable 'Type of offences' and list the real, live-confirmed seeded offence 'Late payment'.</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Source Jurisdiction: Bangladesh, Tax Year: 01 July 2023 - 30 June 2024</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open Interest And Penalties, select Bangladesh / 2023-2024
-2. Verify 'Type of offences' is enabled and lists 'Late payment'</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Selecting Bangladesh / 01 July 2023-30 June 2024 must enable 'Type of offences' and list the real, live-confirmed seeded offence 'Late payment'.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>'Type of offences' correctly listed the real seeded offence for Bangladesh/2023-2024.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'Type of offences' lists the real 'Late payment' offence</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>IAP_06</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Interest And Penalties</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Total days overdue/penalty/interest match an independent calculation</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>With Bangladesh/2023-2024, 'Late payment' offence, Tax due=1,000, Final tax due date=01 Oct 2026, Overdue tax paid=11 Oct 2026: Total days overdue must be 10 (simple calendar day difference), and Total penalty amount/Total interest and penalty must both equal 1,000,000 = PenaltyPerDay(100,000) x 10 days - independently recomputed in Python from the known PenaltyPerDay, not compared to the UI itself.</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Bangladesh/2023-2024, Late payment, Tax due=1000, 01 Oct 2026 -&gt; 11 Oct 2026</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open Interest And Penalties, select Bangladesh/2023-2024/Late payment
-2. Enter Tax due=1000, Final tax due date=01 Oct 2026, Overdue tax paid=11 Oct 2026
-3. Independently compute the expected days/penalty
-4. Verify all 3 computed fields match</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>With Bangladesh/2023-2024, 'Late payment' offence, Tax due=1,000, Final tax due date=01 Oct 2026, Overdue tax paid=11 Oct 2026: Total days overdue must be 10 (simple calendar day difference), and Total penalty amount/Total interest and penalty must both equal 1,000,000 = PenaltyPerDay(100,000) x 10 days - independently recomputed in Python from the known PenaltyPerDay, not compared to the UI itself.</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>All 3 computed fields correctly matched the independent calculation (days=10, penalty=1000000).</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Total days overdue/penalty/interest match the independent calculation</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>IAP_07</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Interest And Penalties</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Outstanding tax due equals Tax due when no advance payment is entered</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>With Tax due=1,000 and 'Tax paid in advance' left blank, Outstanding tax due must equal 1,000.</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Bangladesh/2023-2024/Late payment selected.</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Tax due=1000</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open Interest And Penalties, select Bangladesh/2023-2024/Late payment
-2. Enter Tax due=1000
-3. Verify Outstanding tax due equals 1,000</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>With Tax due=1,000 and 'Tax paid in advance' left blank, Outstanding tax due must equal 1,000.</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Outstanding tax due correctly equals 1000 with no advance payment entered.</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Outstanding tax due equals Tax due with no advance payment</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>IAP_08</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Interest And Penalties</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>'Payment type' offers 'One time payment' and 'Installment' options</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>The 'Interest due' section's 'Payment type' field must offer both 'One time payment' (default) and 'Installment' radio options.</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open Interest And Penalties
-2. Verify both payment type options are visible</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>The 'Interest due' section's 'Payment type' field must offer both 'One time payment' (default) and 'Installment' radio options.</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Both 'Payment type' options are correctly visible.</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Both 'Payment type' options are visible</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>IAP_09</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Interest And Penalties</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Generate Memo/Get Forms/Add to Project become enabled once the calculation completes</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>After a successful Bangladesh/2023-2024/Late payment/1,000/01-11 Oct 2026 calculation, the 3 action buttons must become enabled.</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, full calculation completed.</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open Interest And Penalties, complete a full calculation
-2. Verify the 3 action buttons are enabled</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>After a successful Bangladesh/2023-2024/Late payment/1,000/01-11 Oct 2026 calculation, the 3 action buttons must become enabled.</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>All 3 action buttons correctly became enabled after calculation.</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] All 3 action buttons are enabled after calculation</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>IAP_10</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Interest And Penalties</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Switching to 'By Entity' swaps in Corporate Group fields</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'By Entity' must swap 'Source Jurisdiction' for 'Corporate Group'.</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open Interest And Penalties
-2. Click 'By Entity'
-3. Verify 'Corporate Group' field is visible</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'By Entity' must swap 'Source Jurisdiction' for 'Corporate Group'.</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>Switching to 'By Entity' correctly swapped in the entity-based field.</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'By Entity' mode shows the 'Corporate Group' field</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>IAP_11</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Interest And Penalties</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>'Corporate Group' lists this account's real entity charts</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>In 'By Entity' mode, opening 'Corporate Group' must list this account's real, previously-created entity charts.</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, 'By Entity' mode selected.</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open Interest And Penalties, switch to 'By Entity'
-2. Open 'Corporate Group'
-3. Verify at least one real entity chart is listed</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>In 'By Entity' mode, opening 'Corporate Group' must list this account's real, previously-created entity charts.</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>'Corporate Group' correctly lists 20 real entity chart(s): ['Demo Entity Chart', 'Natmed', 'Empty', 'N', 'Empty Entity Chart', 'Copy of Demo Import Test', 'New Chart with 3rd Party', 'Testing Empty Chart', 'New AG', 'New 3423', 'new', 'testt', 'Royal Enfield Incorporation', 'Test MM', 'new v2', 'Blank', 'JHUMKAH', 'RETRS', 'chuppp', 'BEINTEHA'].</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'Corporate Group' lists at least one real entity chart</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>IAP_12</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Interest And Penalties</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>'Start over' shows a confirmation dialog</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Clicking 'Start over' must show a confirmation dialog reading 'Are you sure to reset all your selections?' with Cancel/Yes actions.</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in.</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Interest And Penalties
 2. Click 'Start over'
 3. Verify the confirmation dialog</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Start over' must show a confirmation dialog reading 'Are you sure to reset all your selections?' with Cancel/Yes actions.</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>'Start over' correctly showed a confirmation dialog before resetting.</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'Start over' shows the expected confirmation dialog</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>IAP_13</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>WTA Calculator - Interest And Penalties</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Confirming 'Start over' (Yes) resets the Source Jurisdiction selection</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Confirming 'Start over' with 'Yes' must reset the Source Jurisdiction select back to its 'Select' placeholder state.</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Bangladesh selected as Source Jurisdiction.</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Source Jurisdiction: Bangladesh</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open Interest And Penalties, select Bangladesh
-2. Click 'Start over' then 'Yes'
-3. Verify Source Jurisdiction resets to 'Select'</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Confirming 'Start over' with 'Yes' must reset the Source Jurisdiction select back to its 'Select' placeholder state.</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>Confirming 'Start over' correctly reset the selection to its placeholder state.</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Source Jurisdiction resets to the 'Select' placeholder</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
